--- a/references/Marketing Process Checklist.xlsx
+++ b/references/Marketing Process Checklist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris-Shiota\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris-Shiota\Desktop\Claude Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28114FEC-3D01-42AD-AD3C-FBF3FDBA0BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981DE72E-DCED-46FC-AF63-27955B3ECBDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{ACA53746-D9CF-4F54-AAF7-CFA8127E2AD3}"/>
+    <workbookView xWindow="30612" yWindow="-15048" windowWidth="17496" windowHeight="30216" xr2:uid="{ACA53746-D9CF-4F54-AAF7-CFA8127E2AD3}"/>
   </bookViews>
   <sheets>
     <sheet name="Marketing Process Tracking" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="195">
   <si>
     <t>Initial Checklist</t>
   </si>
@@ -622,6 +622,18 @@
   </si>
   <si>
     <t>See Issues Tab (see design on that tab with Consultant roster and key dates below), PDF Report and Send to those checked on deal team from Roster Report.</t>
+  </si>
+  <si>
+    <t>Finalize B&amp;F Group and Counter Terms</t>
+  </si>
+  <si>
+    <t>Send out B&amp;F</t>
+  </si>
+  <si>
+    <t>Create B&amp;F Recommendation - Pro Con of each Offer</t>
+  </si>
+  <si>
+    <t>Buyer Interviews</t>
   </si>
 </sst>
 </file>
@@ -662,12 +674,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -696,8 +714,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1034,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D97CACF6-7D67-40EF-A18D-D0F807BA93CE}">
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1215,12 +1233,12 @@
       </c>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="2:6" s="7" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
+    <row r="21" spans="2:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
     </row>
     <row r="22" spans="2:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
@@ -1544,157 +1562,204 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>47</v>
+      <c r="B52" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C52" s="7"/>
+      <c r="D52" s="8" t="s">
+        <v>183</v>
       </c>
       <c r="E52" s="1"/>
     </row>
     <row r="53" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
-        <v>33</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>47</v>
+      <c r="B53" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C53" s="7"/>
+      <c r="D53" s="8" t="s">
+        <v>183</v>
       </c>
       <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D54" s="1"/>
+      <c r="B54" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8" t="s">
+        <v>183</v>
+      </c>
       <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>34</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D55" s="1"/>
+      <c r="B55" t="s">
+        <v>193</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>183</v>
+      </c>
       <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="E56" s="1"/>
     </row>
     <row r="57" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>189</v>
+        <v>47</v>
       </c>
       <c r="E57" s="1"/>
-      <c r="F57" s="1" t="s">
-        <v>157</v>
-      </c>
     </row>
     <row r="58" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" t="s">
-        <v>37</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>187</v>
-      </c>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
     </row>
     <row r="59" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" t="s">
-        <v>38</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="D59" s="1"/>
       <c r="E59" s="1"/>
     </row>
     <row r="60" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" t="s">
-        <v>39</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="D60" s="1"/>
       <c r="E60" s="1"/>
     </row>
-    <row r="61" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
-        <v>43</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>190</v>
-      </c>
+    <row r="61" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>34</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D61" s="1"/>
       <c r="E61" s="1"/>
     </row>
     <row r="62" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E62" s="1"/>
     </row>
     <row r="63" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>41</v>
+        <v>158</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>92</v>
+        <v>189</v>
       </c>
       <c r="E63" s="1"/>
+      <c r="F63" s="1" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="64" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E64" s="1"/>
+        <v>188</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="65" spans="2:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="E65" s="1"/>
     </row>
     <row r="66" spans="2:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
+        <v>39</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E66" s="1"/>
+    </row>
+    <row r="67" spans="2:5" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>43</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E67" s="1"/>
+    </row>
+    <row r="68" spans="2:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>40</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E68" s="1"/>
+    </row>
+    <row r="69" spans="2:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>41</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E69" s="1"/>
+    </row>
+    <row r="70" spans="2:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>89</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E70" s="1"/>
+    </row>
+    <row r="71" spans="2:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>90</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E71" s="1"/>
+    </row>
+    <row r="72" spans="2:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
         <v>91</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E66" s="1"/>
-    </row>
-    <row r="67" spans="2:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-    </row>
-    <row r="68" spans="2:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-    </row>
-    <row r="69" spans="2:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E69" s="1"/>
-    </row>
-    <row r="70" spans="2:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E70" s="1"/>
-    </row>
-    <row r="71" spans="2:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E71" s="1"/>
+      <c r="E72" s="1"/>
+    </row>
+    <row r="73" spans="2:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+    </row>
+    <row r="74" spans="2:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+    </row>
+    <row r="75" spans="2:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E75" s="1"/>
+    </row>
+    <row r="76" spans="2:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E76" s="1"/>
+    </row>
+    <row r="77" spans="2:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E77" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
